--- a/app/static/WSFL_FAQs_REVISED.xlsx
+++ b/app/static/WSFL_FAQs_REVISED.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stella\Documents\flask-dev\flask-wsfl-app\app\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stell\flask-wsfl-app\flask-wsfl-app\app\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3372A3-D527-4B4D-84EF-B2A52ABDC584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953EC26D-51CA-4155-95BE-D6D3064BAE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="210" windowWidth="15170" windowHeight="14110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FAQ" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="102">
   <si>
     <t>Question Type</t>
   </si>
@@ -319,6 +319,32 @@
   </si>
   <si>
     <t>privacy, NSN, permissions, access, reporting</t>
+  </si>
+  <si>
+    <t>Reason 1: Students are also in another class for the same term and year&lt;br&gt;
+If all students in a class are also recorded in another class for the same term and year, this can occur when:&lt;br&gt;
+• a class list has been uploaded more than once, or&lt;br&gt;
+• there is overlap between classes&lt;br&gt;&lt;br&gt;
+If you think this may be the case, check your Missing Classes Report.&lt;br&gt;
+If the class is not listed, no further action is required.&lt;br&gt;
+Students will still only be counted once, even if they appear in multiple classes.&lt;br&gt;&lt;br&gt;
+Reason 2: No new achievement data was uploaded&lt;br&gt;
+If you downloaded a class file from Class Lookup and re-uploaded it without adding any new competencies, no changes will be recorded.&lt;br&gt;
+This means:&lt;br&gt;
+• the class will still appear as movable, and&lt;br&gt;
+• no progress has been detected for that term&lt;br&gt;&lt;br&gt;
+Next steps:&lt;br&gt;
+• Check that the student achievements in your file are correct&lt;br&gt;
+• Confirm whether any students have learned new skills this term&lt;br&gt;
+• Make sure you uploaded the updated file, not the original download&lt;br&gt;&lt;br&gt;
+If no students have progressed, talk to the provider to understand why no progress was made so you can include this in your funder report.&lt;br&gt;
+If there are missing achievements, update your file and re-upload it, or record them directly in the Class Lookup tool.&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Why isn’t my class showing progress for this term?</t>
+  </si>
+  <si>
+    <t>missing data, class with no progress</t>
   </si>
 </sst>
 </file>
@@ -661,13 +687,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -681,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -695,7 +721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -709,7 +735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -723,7 +749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -737,7 +763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -751,7 +777,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -765,7 +791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -779,7 +805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -793,7 +819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -807,7 +833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -821,7 +847,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -835,7 +861,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -849,7 +875,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -863,7 +889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -877,7 +903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -891,7 +917,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -905,7 +931,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -919,7 +945,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -933,7 +959,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -947,7 +973,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -961,7 +987,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -975,7 +1001,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -989,7 +1015,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1003,7 +1029,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1017,7 +1043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -1031,7 +1057,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -1045,7 +1071,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -1059,7 +1085,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -1073,7 +1099,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -1085,6 +1111,20 @@
       </c>
       <c r="D30" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
